--- a/research/traditional_assets/database/data/iceland/iceland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09789999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="E2">
-        <v>0.66</v>
+        <v>-0.0338</v>
       </c>
       <c r="G2">
-        <v>0.07975460122699386</v>
+        <v>0.3800340328984685</v>
       </c>
       <c r="H2">
-        <v>0.07975460122699386</v>
+        <v>0.3800340328984685</v>
       </c>
       <c r="I2">
-        <v>0.2797546012269939</v>
+        <v>0.07884288145207033</v>
       </c>
       <c r="J2">
-        <v>0.2700043305665825</v>
+        <v>0.07622251509792799</v>
       </c>
       <c r="K2">
-        <v>65.7</v>
+        <v>9.9</v>
       </c>
       <c r="L2">
-        <v>0.2687116564417178</v>
+        <v>0.05615428247305729</v>
       </c>
       <c r="M2">
-        <v>24.6</v>
+        <v>31.29</v>
       </c>
       <c r="N2">
-        <v>0.08556521739130435</v>
+        <v>0.1502881844380403</v>
       </c>
       <c r="O2">
-        <v>0.3744292237442922</v>
+        <v>3.16060606060606</v>
       </c>
       <c r="P2">
-        <v>12.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q2">
-        <v>0.04278260869565217</v>
+        <v>0.1162343900096062</v>
       </c>
       <c r="R2">
-        <v>0.1872146118721461</v>
+        <v>2.444444444444444</v>
       </c>
       <c r="S2">
-        <v>12.3</v>
+        <v>7.09</v>
       </c>
       <c r="T2">
-        <v>0.5</v>
+        <v>0.2265899648449984</v>
       </c>
       <c r="U2">
-        <v>10.2</v>
+        <v>14.6</v>
       </c>
       <c r="V2">
-        <v>0.03547826086956522</v>
+        <v>0.07012487992315082</v>
       </c>
       <c r="W2">
-        <v>0.5994525547445256</v>
+        <v>0.06277742549143944</v>
       </c>
       <c r="X2">
-        <v>0.05784456177545363</v>
+        <v>0.09522887319797657</v>
       </c>
       <c r="Y2">
-        <v>0.541607992969072</v>
+        <v>-0.03245144770653713</v>
       </c>
       <c r="Z2">
-        <v>1.860164333536214</v>
+        <v>1.001704545454545</v>
       </c>
       <c r="AA2">
-        <v>0.5022524256202786</v>
+        <v>0.0763524398395722</v>
       </c>
       <c r="AB2">
-        <v>0.05483265134409854</v>
+        <v>0.08955482257723495</v>
       </c>
       <c r="AC2">
-        <v>0.4474197742761801</v>
+        <v>-0.01320238273766275</v>
       </c>
       <c r="AD2">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="AG2">
-        <v>18.3</v>
+        <v>12.6</v>
       </c>
       <c r="AH2">
-        <v>0.09018987341772151</v>
+        <v>0.1155480033984707</v>
       </c>
       <c r="AI2">
-        <v>0.1530612244897959</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="AJ2">
-        <v>0.05984303466317855</v>
+        <v>0.05706521739130435</v>
       </c>
       <c r="AK2">
-        <v>0.1039772727272727</v>
+        <v>0.09452363090772692</v>
       </c>
       <c r="AL2">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="AM2">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="AN2">
-        <v>0.4019746121297602</v>
+        <v>1.850340136054422</v>
       </c>
       <c r="AO2">
-        <v>28.14814814814815</v>
+        <v>4.100294985250738</v>
       </c>
       <c r="AP2">
-        <v>0.2581100141043723</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="AQ2">
-        <v>28.14814814814815</v>
+        <v>4.100294985250738</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09789999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="E3">
-        <v>0.66</v>
+        <v>-0.0338</v>
       </c>
       <c r="G3">
-        <v>0.07975460122699386</v>
+        <v>0.3800340328984685</v>
       </c>
       <c r="H3">
-        <v>0.07975460122699386</v>
+        <v>0.3800340328984685</v>
       </c>
       <c r="I3">
-        <v>0.2797546012269939</v>
+        <v>0.07884288145207033</v>
       </c>
       <c r="J3">
-        <v>0.2700043305665825</v>
+        <v>0.07622251509792799</v>
       </c>
       <c r="K3">
-        <v>65.7</v>
+        <v>9.9</v>
       </c>
       <c r="L3">
-        <v>0.2687116564417178</v>
+        <v>0.05615428247305729</v>
       </c>
       <c r="M3">
-        <v>24.6</v>
+        <v>31.29</v>
       </c>
       <c r="N3">
-        <v>0.08556521739130435</v>
+        <v>0.1502881844380403</v>
       </c>
       <c r="O3">
-        <v>0.3744292237442922</v>
+        <v>3.16060606060606</v>
       </c>
       <c r="P3">
-        <v>12.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q3">
-        <v>0.04278260869565217</v>
+        <v>0.1162343900096062</v>
       </c>
       <c r="R3">
-        <v>0.1872146118721461</v>
+        <v>2.444444444444444</v>
       </c>
       <c r="S3">
-        <v>12.3</v>
+        <v>7.09</v>
       </c>
       <c r="T3">
-        <v>0.5</v>
+        <v>0.2265899648449984</v>
       </c>
       <c r="U3">
-        <v>10.2</v>
+        <v>14.6</v>
       </c>
       <c r="V3">
-        <v>0.03547826086956522</v>
+        <v>0.07012487992315082</v>
       </c>
       <c r="W3">
-        <v>0.5994525547445256</v>
+        <v>0.06277742549143944</v>
       </c>
       <c r="X3">
-        <v>0.05784456177545363</v>
+        <v>0.09522887319797657</v>
       </c>
       <c r="Y3">
-        <v>0.541607992969072</v>
+        <v>-0.03245144770653713</v>
       </c>
       <c r="Z3">
-        <v>1.860164333536214</v>
+        <v>1.001704545454545</v>
       </c>
       <c r="AA3">
-        <v>0.5022524256202786</v>
+        <v>0.0763524398395722</v>
       </c>
       <c r="AB3">
-        <v>0.05483265134409854</v>
+        <v>0.08955482257723495</v>
       </c>
       <c r="AC3">
-        <v>0.4474197742761801</v>
+        <v>-0.01320238273766275</v>
       </c>
       <c r="AD3">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="AG3">
-        <v>18.3</v>
+        <v>12.6</v>
       </c>
       <c r="AH3">
-        <v>0.09018987341772151</v>
+        <v>0.1155480033984707</v>
       </c>
       <c r="AI3">
-        <v>0.1530612244897959</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="AJ3">
-        <v>0.05984303466317855</v>
+        <v>0.05706521739130435</v>
       </c>
       <c r="AK3">
-        <v>0.1039772727272727</v>
+        <v>0.09452363090772692</v>
       </c>
       <c r="AL3">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="AM3">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="AN3">
-        <v>0.4019746121297602</v>
+        <v>1.850340136054422</v>
       </c>
       <c r="AO3">
-        <v>28.14814814814815</v>
+        <v>4.100294985250738</v>
       </c>
       <c r="AP3">
-        <v>0.2581100141043723</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="AQ3">
-        <v>28.14814814814815</v>
+        <v>4.100294985250738</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/iceland/iceland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.034</v>
+        <v>0.0395</v>
       </c>
       <c r="E2">
-        <v>-0.0338</v>
+        <v>0.0192</v>
       </c>
       <c r="G2">
-        <v>0.3800340328984685</v>
+        <v>0.04997597308986065</v>
       </c>
       <c r="H2">
-        <v>0.3800340328984685</v>
+        <v>0.04997597308986065</v>
       </c>
       <c r="I2">
-        <v>0.07884288145207033</v>
+        <v>0.09370494954348871</v>
       </c>
       <c r="J2">
-        <v>0.07622251509792799</v>
+        <v>0.0869559621061303</v>
       </c>
       <c r="K2">
-        <v>9.9</v>
+        <v>15.7</v>
       </c>
       <c r="L2">
-        <v>0.05615428247305729</v>
+        <v>0.07544449783757809</v>
       </c>
       <c r="M2">
-        <v>31.29</v>
+        <v>13.88</v>
       </c>
       <c r="N2">
-        <v>0.1502881844380403</v>
+        <v>0.0579782790309106</v>
       </c>
       <c r="O2">
-        <v>3.16060606060606</v>
+        <v>0.8840764331210191</v>
       </c>
       <c r="P2">
-        <v>24.2</v>
+        <v>6.84</v>
       </c>
       <c r="Q2">
-        <v>0.1162343900096062</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="R2">
-        <v>2.444444444444444</v>
+        <v>0.4356687898089172</v>
       </c>
       <c r="S2">
-        <v>7.09</v>
+        <v>7.039999999999999</v>
       </c>
       <c r="T2">
-        <v>0.2265899648449984</v>
+        <v>0.5072046109510087</v>
       </c>
       <c r="U2">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="V2">
-        <v>0.07012487992315082</v>
+        <v>0.06641604010025062</v>
       </c>
       <c r="W2">
-        <v>0.06277742549143944</v>
+        <v>0.1300745650372825</v>
       </c>
       <c r="X2">
-        <v>0.09522887319797657</v>
+        <v>0.08117348556088365</v>
       </c>
       <c r="Y2">
-        <v>-0.03245144770653713</v>
+        <v>0.04890107947639886</v>
       </c>
       <c r="Z2">
-        <v>1.001704545454545</v>
+        <v>1.561140285071268</v>
       </c>
       <c r="AA2">
-        <v>0.0763524398395722</v>
+        <v>0.1357504554710106</v>
       </c>
       <c r="AB2">
-        <v>0.08955482257723495</v>
+        <v>0.07700558419347545</v>
       </c>
       <c r="AC2">
-        <v>-0.01320238273766275</v>
+        <v>0.05874487127753517</v>
       </c>
       <c r="AD2">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="AG2">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
       <c r="AH2">
-        <v>0.1155480033984707</v>
+        <v>0.1103678929765886</v>
       </c>
       <c r="AI2">
-        <v>0.1839080459770115</v>
+        <v>0.1870277078085643</v>
       </c>
       <c r="AJ2">
-        <v>0.05706521739130435</v>
+        <v>0.05450236966824644</v>
       </c>
       <c r="AK2">
-        <v>0.09452363090772692</v>
+        <v>0.09657102869139257</v>
       </c>
       <c r="AL2">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="AM2">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="AN2">
-        <v>1.850340136054422</v>
+        <v>1.441747572815534</v>
       </c>
       <c r="AO2">
-        <v>4.100294985250738</v>
+        <v>5.508474576271186</v>
       </c>
       <c r="AP2">
-        <v>0.8571428571428572</v>
+        <v>0.6699029126213591</v>
       </c>
       <c r="AQ2">
-        <v>4.100294985250738</v>
+        <v>5.508474576271186</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.034</v>
+        <v>0.0395</v>
       </c>
       <c r="E3">
-        <v>-0.0338</v>
+        <v>0.0192</v>
       </c>
       <c r="G3">
-        <v>0.3800340328984685</v>
+        <v>0.04997597308986065</v>
       </c>
       <c r="H3">
-        <v>0.3800340328984685</v>
+        <v>0.04997597308986065</v>
       </c>
       <c r="I3">
-        <v>0.07884288145207033</v>
+        <v>0.09370494954348871</v>
       </c>
       <c r="J3">
-        <v>0.07622251509792799</v>
+        <v>0.0869559621061303</v>
       </c>
       <c r="K3">
-        <v>9.9</v>
+        <v>15.7</v>
       </c>
       <c r="L3">
-        <v>0.05615428247305729</v>
+        <v>0.07544449783757809</v>
       </c>
       <c r="M3">
-        <v>31.29</v>
+        <v>13.88</v>
       </c>
       <c r="N3">
-        <v>0.1502881844380403</v>
+        <v>0.0579782790309106</v>
       </c>
       <c r="O3">
-        <v>3.16060606060606</v>
+        <v>0.8840764331210191</v>
       </c>
       <c r="P3">
-        <v>24.2</v>
+        <v>6.84</v>
       </c>
       <c r="Q3">
-        <v>0.1162343900096062</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="R3">
-        <v>2.444444444444444</v>
+        <v>0.4356687898089172</v>
       </c>
       <c r="S3">
-        <v>7.09</v>
+        <v>7.039999999999999</v>
       </c>
       <c r="T3">
-        <v>0.2265899648449984</v>
+        <v>0.5072046109510087</v>
       </c>
       <c r="U3">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="V3">
-        <v>0.07012487992315082</v>
+        <v>0.06641604010025062</v>
       </c>
       <c r="W3">
-        <v>0.06277742549143944</v>
+        <v>0.1300745650372825</v>
       </c>
       <c r="X3">
-        <v>0.09522887319797657</v>
+        <v>0.08117348556088365</v>
       </c>
       <c r="Y3">
-        <v>-0.03245144770653713</v>
+        <v>0.04890107947639886</v>
       </c>
       <c r="Z3">
-        <v>1.001704545454545</v>
+        <v>1.561140285071268</v>
       </c>
       <c r="AA3">
-        <v>0.0763524398395722</v>
+        <v>0.1357504554710106</v>
       </c>
       <c r="AB3">
-        <v>0.08955482257723495</v>
+        <v>0.07700558419347545</v>
       </c>
       <c r="AC3">
-        <v>-0.01320238273766275</v>
+        <v>0.05874487127753517</v>
       </c>
       <c r="AD3">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="AG3">
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
       <c r="AH3">
-        <v>0.1155480033984707</v>
+        <v>0.1103678929765886</v>
       </c>
       <c r="AI3">
-        <v>0.1839080459770115</v>
+        <v>0.1870277078085643</v>
       </c>
       <c r="AJ3">
-        <v>0.05706521739130435</v>
+        <v>0.05450236966824644</v>
       </c>
       <c r="AK3">
-        <v>0.09452363090772692</v>
+        <v>0.09657102869139257</v>
       </c>
       <c r="AL3">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="AM3">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="AN3">
-        <v>1.850340136054422</v>
+        <v>1.441747572815534</v>
       </c>
       <c r="AO3">
-        <v>4.100294985250738</v>
+        <v>5.508474576271186</v>
       </c>
       <c r="AP3">
-        <v>0.8571428571428572</v>
+        <v>0.6699029126213591</v>
       </c>
       <c r="AQ3">
-        <v>4.100294985250738</v>
+        <v>5.508474576271186</v>
       </c>
     </row>
   </sheetData>
